--- a/artfynd/A 1481-2026 artfynd.xlsx
+++ b/artfynd/A 1481-2026 artfynd.xlsx
@@ -7935,7 +7935,7 @@
         <v>130849489</v>
       </c>
       <c r="B74" t="n">
-        <v>80351</v>
+        <v>80352</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>

--- a/artfynd/A 1481-2026 artfynd.xlsx
+++ b/artfynd/A 1481-2026 artfynd.xlsx
@@ -7935,7 +7935,7 @@
         <v>130849489</v>
       </c>
       <c r="B74" t="n">
-        <v>80352</v>
+        <v>80354</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>

--- a/artfynd/A 1481-2026 artfynd.xlsx
+++ b/artfynd/A 1481-2026 artfynd.xlsx
@@ -7935,7 +7935,7 @@
         <v>130849489</v>
       </c>
       <c r="B74" t="n">
-        <v>80354</v>
+        <v>80355</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>

--- a/artfynd/A 1481-2026 artfynd.xlsx
+++ b/artfynd/A 1481-2026 artfynd.xlsx
@@ -7935,7 +7935,7 @@
         <v>130849489</v>
       </c>
       <c r="B74" t="n">
-        <v>80355</v>
+        <v>80356</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>

--- a/artfynd/A 1481-2026 artfynd.xlsx
+++ b/artfynd/A 1481-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY85"/>
+  <dimension ref="A1:AY87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130803092</v>
+        <v>130803065</v>
       </c>
       <c r="B2" t="n">
-        <v>89193</v>
+        <v>91859</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>510</v>
+        <v>112</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>424832</v>
+        <v>424740</v>
       </c>
       <c r="R2" t="n">
-        <v>6712186</v>
+        <v>6712346</v>
       </c>
       <c r="S2" t="n">
         <v>20</v>
@@ -760,22 +760,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130803083</v>
+        <v>131887913</v>
       </c>
       <c r="B3" t="n">
-        <v>83089</v>
+        <v>85592</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,37 +783,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1312</v>
+        <v>241</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Gransotdyna</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Camarops tubulina</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Alb. &amp; Schwein.) Shear</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Östra utsjö, Dlr</t>
+          <t>Nordvallen, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>424802</v>
+        <v>424733</v>
       </c>
       <c r="R3" t="n">
-        <v>6712148</v>
+        <v>6712369</v>
       </c>
       <c r="S3" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -837,12 +837,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2026-03-22</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2026-03-22</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -851,63 +851,67 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130803039</v>
+        <v>130803072</v>
       </c>
       <c r="B4" t="n">
-        <v>83223</v>
+        <v>83292</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6440</v>
+        <v>306</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Kornig nållav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenotheca chlorella</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Östra utsjö, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>424963</v>
+        <v>424874</v>
       </c>
       <c r="R4" t="n">
-        <v>6712076</v>
+        <v>6712055</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -948,66 +952,64 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130803040</v>
+        <v>130803093</v>
       </c>
       <c r="B5" t="n">
-        <v>91876</v>
+        <v>83299</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5447</v>
+        <v>308</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Östra utsjö, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>424793</v>
+        <v>424928</v>
       </c>
       <c r="R5" t="n">
-        <v>6712247</v>
+        <v>6712167</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1048,7 +1050,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1067,10 +1068,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130803069</v>
+        <v>130803094</v>
       </c>
       <c r="B6" t="n">
-        <v>81228</v>
+        <v>83299</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1078,21 +1079,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1049</v>
+        <v>308</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1102,10 +1103,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>424815</v>
+        <v>424750</v>
       </c>
       <c r="R6" t="n">
-        <v>6712165</v>
+        <v>6712387</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1152,22 +1153,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130803088</v>
+        <v>130803095</v>
       </c>
       <c r="B7" t="n">
-        <v>83089</v>
+        <v>83299</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1175,21 +1176,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1312</v>
+        <v>308</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1199,10 +1200,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>424964</v>
+        <v>424724</v>
       </c>
       <c r="R7" t="n">
-        <v>6712067</v>
+        <v>6712378</v>
       </c>
       <c r="S7" t="n">
         <v>20</v>
@@ -1249,22 +1250,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130803067</v>
+        <v>130803096</v>
       </c>
       <c r="B8" t="n">
-        <v>78255</v>
+        <v>83299</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1272,21 +1273,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>228579</v>
+        <v>308</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1296,10 +1297,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>424814</v>
+        <v>424792</v>
       </c>
       <c r="R8" t="n">
-        <v>6712361</v>
+        <v>6712252</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>
@@ -1346,44 +1347,44 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130803042</v>
+        <v>130803097</v>
       </c>
       <c r="B9" t="n">
-        <v>91771</v>
+        <v>83299</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5447</v>
+        <v>308</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1393,10 +1394,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>424979</v>
+        <v>424765</v>
       </c>
       <c r="R9" t="n">
-        <v>6712092</v>
+        <v>6712208</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1443,44 +1444,44 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130803071</v>
+        <v>130803098</v>
       </c>
       <c r="B10" t="n">
-        <v>91181</v>
+        <v>83299</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5685</v>
+        <v>308</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gullgröppa</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pseudomerulius aureus</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Jülich</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1490,10 +1491,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>424873</v>
+        <v>424798</v>
       </c>
       <c r="R10" t="n">
-        <v>6712126</v>
+        <v>6712176</v>
       </c>
       <c r="S10" t="n">
         <v>20</v>
@@ -1540,22 +1541,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130803064</v>
+        <v>130803099</v>
       </c>
       <c r="B11" t="n">
-        <v>91829</v>
+        <v>83299</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1563,21 +1564,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5442</v>
+        <v>308</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1587,10 +1588,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>424893</v>
+        <v>424969</v>
       </c>
       <c r="R11" t="n">
-        <v>6712101</v>
+        <v>6712078</v>
       </c>
       <c r="S11" t="n">
         <v>20</v>
@@ -1637,44 +1638,44 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130803066</v>
+        <v>130803100</v>
       </c>
       <c r="B12" t="n">
-        <v>75221</v>
+        <v>83299</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6428</v>
+        <v>308</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1684,10 +1685,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>424814</v>
+        <v>424965</v>
       </c>
       <c r="R12" t="n">
-        <v>6712218</v>
+        <v>6712084</v>
       </c>
       <c r="S12" t="n">
         <v>20</v>
@@ -1734,22 +1735,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130803085</v>
+        <v>131887961</v>
       </c>
       <c r="B13" t="n">
-        <v>83089</v>
+        <v>83350</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1757,37 +1758,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1312</v>
+        <v>308</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Östra utsjö, Dlr</t>
+          <t>Nordvallen, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>424798</v>
+        <v>424831</v>
       </c>
       <c r="R13" t="n">
-        <v>6712168</v>
+        <v>6712360</v>
       </c>
       <c r="S13" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1811,12 +1812,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2026-03-22</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2026-03-22</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1831,60 +1832,60 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130803041</v>
+        <v>131887962</v>
       </c>
       <c r="B14" t="n">
-        <v>91771</v>
+        <v>83350</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5447</v>
+        <v>308</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Östra utsjö, Dlr</t>
+          <t>Nordvallen, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>424881</v>
+        <v>424920</v>
       </c>
       <c r="R14" t="n">
-        <v>6712113</v>
+        <v>6712232</v>
       </c>
       <c r="S14" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1908,12 +1909,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2026-03-22</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2026-03-22</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1928,22 +1929,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130803074</v>
+        <v>131887967</v>
       </c>
       <c r="B15" t="n">
-        <v>79243</v>
+        <v>83350</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1951,37 +1952,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>308</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Östra utsjö, Dlr</t>
+          <t>Nordvallen, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>424801</v>
+        <v>424723</v>
       </c>
       <c r="R15" t="n">
-        <v>6712403</v>
+        <v>6712381</v>
       </c>
       <c r="S15" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2005,12 +2006,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2026-03-22</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2026-03-22</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2025,22 +2026,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130803065</v>
+        <v>130803068</v>
       </c>
       <c r="B16" t="n">
-        <v>91758</v>
+        <v>89292</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2048,21 +2049,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>112</v>
+        <v>510</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2072,10 +2073,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>424740</v>
+        <v>424990</v>
       </c>
       <c r="R16" t="n">
-        <v>6712346</v>
+        <v>6712084</v>
       </c>
       <c r="S16" t="n">
         <v>20</v>
@@ -2122,22 +2123,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130803084</v>
+        <v>130803092</v>
       </c>
       <c r="B17" t="n">
-        <v>83089</v>
+        <v>89292</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2145,21 +2146,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1312</v>
+        <v>510</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2169,10 +2170,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>424817</v>
+        <v>424832</v>
       </c>
       <c r="R17" t="n">
-        <v>6712153</v>
+        <v>6712186</v>
       </c>
       <c r="S17" t="n">
         <v>20</v>
@@ -2219,22 +2220,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130803036</v>
+        <v>130803069</v>
       </c>
       <c r="B18" t="n">
-        <v>83223</v>
+        <v>81312</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2242,21 +2243,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6440</v>
+        <v>1049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2266,10 +2267,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>424756</v>
+        <v>424815</v>
       </c>
       <c r="R18" t="n">
-        <v>6712130</v>
+        <v>6712165</v>
       </c>
       <c r="S18" t="n">
         <v>20</v>
@@ -2316,22 +2317,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130803073</v>
+        <v>130848919</v>
       </c>
       <c r="B19" t="n">
-        <v>79243</v>
+        <v>81312</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2339,34 +2340,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>1049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Östra utsjö, Dlr</t>
+          <t>Nordvallen, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>424873</v>
+        <v>424721</v>
       </c>
       <c r="R19" t="n">
-        <v>6712251</v>
+        <v>6712550</v>
       </c>
       <c r="S19" t="n">
         <v>20</v>
@@ -2393,12 +2394,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2413,22 +2414,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130803096</v>
+        <v>130848920</v>
       </c>
       <c r="B20" t="n">
-        <v>83215</v>
+        <v>81312</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2436,34 +2437,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>308</v>
+        <v>1049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Östra utsjö, Dlr</t>
+          <t>Nordvallen, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>424792</v>
+        <v>424620</v>
       </c>
       <c r="R20" t="n">
-        <v>6712252</v>
+        <v>6712420</v>
       </c>
       <c r="S20" t="n">
         <v>20</v>
@@ -2490,12 +2491,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2510,22 +2511,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130803093</v>
+        <v>130848921</v>
       </c>
       <c r="B21" t="n">
-        <v>83215</v>
+        <v>81312</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2533,34 +2534,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>308</v>
+        <v>1049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Östra utsjö, Dlr</t>
+          <t>Nordvallen, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>424928</v>
+        <v>424593</v>
       </c>
       <c r="R21" t="n">
-        <v>6712167</v>
+        <v>6712411</v>
       </c>
       <c r="S21" t="n">
         <v>20</v>
@@ -2587,12 +2588,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2607,22 +2608,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130803094</v>
+        <v>130848922</v>
       </c>
       <c r="B22" t="n">
-        <v>83215</v>
+        <v>81312</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2630,34 +2631,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>308</v>
+        <v>1049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Östra utsjö, Dlr</t>
+          <t>Nordvallen, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>424750</v>
+        <v>424576</v>
       </c>
       <c r="R22" t="n">
-        <v>6712387</v>
+        <v>6712311</v>
       </c>
       <c r="S22" t="n">
         <v>20</v>
@@ -2684,12 +2685,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2704,57 +2705,57 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130803043</v>
+        <v>130848915</v>
       </c>
       <c r="B23" t="n">
-        <v>92530</v>
+        <v>92369</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>3298</v>
+        <v>1209</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Östra utsjö, Dlr</t>
+          <t>Nordvallen, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>424756</v>
+        <v>424738</v>
       </c>
       <c r="R23" t="n">
-        <v>6712113</v>
+        <v>6712212</v>
       </c>
       <c r="S23" t="n">
         <v>20</v>
@@ -2781,12 +2782,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2801,22 +2802,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130803086</v>
+        <v>130803080</v>
       </c>
       <c r="B24" t="n">
-        <v>83089</v>
+        <v>83173</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2848,10 +2849,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>424812</v>
+        <v>424918</v>
       </c>
       <c r="R24" t="n">
-        <v>6712226</v>
+        <v>6712188</v>
       </c>
       <c r="S24" t="n">
         <v>20</v>
@@ -2898,22 +2899,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130803097</v>
+        <v>130803081</v>
       </c>
       <c r="B25" t="n">
-        <v>83215</v>
+        <v>83173</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2921,21 +2922,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>308</v>
+        <v>1312</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2945,10 +2946,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>424765</v>
+        <v>424813</v>
       </c>
       <c r="R25" t="n">
-        <v>6712208</v>
+        <v>6712360</v>
       </c>
       <c r="S25" t="n">
         <v>20</v>
@@ -2995,60 +2996,57 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130803072</v>
+        <v>130803082</v>
       </c>
       <c r="B26" t="n">
-        <v>83208</v>
+        <v>83173</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>306</v>
+        <v>1312</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kornig nållav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Chaenotheca chlorella</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Östra utsjö, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>424874</v>
+        <v>424785</v>
       </c>
       <c r="R26" t="n">
-        <v>6712055</v>
+        <v>6712249</v>
       </c>
       <c r="S26" t="n">
         <v>20</v>
@@ -3089,29 +3087,28 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130803099</v>
+        <v>130803083</v>
       </c>
       <c r="B27" t="n">
-        <v>83215</v>
+        <v>83173</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3119,21 +3116,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>308</v>
+        <v>1312</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3143,10 +3140,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>424969</v>
+        <v>424802</v>
       </c>
       <c r="R27" t="n">
-        <v>6712078</v>
+        <v>6712148</v>
       </c>
       <c r="S27" t="n">
         <v>20</v>
@@ -3193,22 +3190,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130803037</v>
+        <v>130803084</v>
       </c>
       <c r="B28" t="n">
-        <v>83223</v>
+        <v>83173</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3216,21 +3213,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6440</v>
+        <v>1312</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3240,10 +3237,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>424874</v>
+        <v>424817</v>
       </c>
       <c r="R28" t="n">
-        <v>6712082</v>
+        <v>6712153</v>
       </c>
       <c r="S28" t="n">
         <v>20</v>
@@ -3290,22 +3287,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130803087</v>
+        <v>130803085</v>
       </c>
       <c r="B29" t="n">
-        <v>83089</v>
+        <v>83173</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3337,10 +3334,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>424963</v>
+        <v>424798</v>
       </c>
       <c r="R29" t="n">
-        <v>6712072</v>
+        <v>6712168</v>
       </c>
       <c r="S29" t="n">
         <v>20</v>
@@ -3387,22 +3384,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130803080</v>
+        <v>130803086</v>
       </c>
       <c r="B30" t="n">
-        <v>83089</v>
+        <v>83173</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3434,10 +3431,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>424918</v>
+        <v>424812</v>
       </c>
       <c r="R30" t="n">
-        <v>6712188</v>
+        <v>6712226</v>
       </c>
       <c r="S30" t="n">
         <v>20</v>
@@ -3484,22 +3481,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130803079</v>
+        <v>130803087</v>
       </c>
       <c r="B31" t="n">
-        <v>79243</v>
+        <v>83173</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3507,21 +3504,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3531,10 +3528,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>424980</v>
+        <v>424963</v>
       </c>
       <c r="R31" t="n">
-        <v>6712107</v>
+        <v>6712072</v>
       </c>
       <c r="S31" t="n">
         <v>20</v>
@@ -3581,22 +3578,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130803098</v>
+        <v>130803088</v>
       </c>
       <c r="B32" t="n">
-        <v>83215</v>
+        <v>83173</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3604,21 +3601,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>308</v>
+        <v>1312</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3628,10 +3625,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>424798</v>
+        <v>424964</v>
       </c>
       <c r="R32" t="n">
-        <v>6712176</v>
+        <v>6712067</v>
       </c>
       <c r="S32" t="n">
         <v>20</v>
@@ -3678,22 +3675,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130803081</v>
+        <v>130849489</v>
       </c>
       <c r="B33" t="n">
-        <v>83089</v>
+        <v>80433</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3701,34 +3698,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1312</v>
+        <v>2081</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Östra utsjö, Dlr</t>
+          <t>Nordvallen, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>424813</v>
+        <v>424637</v>
       </c>
       <c r="R33" t="n">
-        <v>6712360</v>
+        <v>6712469</v>
       </c>
       <c r="S33" t="n">
         <v>20</v>
@@ -3755,12 +3752,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3775,44 +3772,44 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130803077</v>
+        <v>130803043</v>
       </c>
       <c r="B34" t="n">
-        <v>79243</v>
+        <v>92632</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3822,10 +3819,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>424877</v>
+        <v>424756</v>
       </c>
       <c r="R34" t="n">
-        <v>6712121</v>
+        <v>6712113</v>
       </c>
       <c r="S34" t="n">
         <v>20</v>
@@ -3872,22 +3869,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130803078</v>
+        <v>130803064</v>
       </c>
       <c r="B35" t="n">
-        <v>79243</v>
+        <v>91930</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3895,21 +3892,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3919,10 +3916,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>424951</v>
+        <v>424893</v>
       </c>
       <c r="R35" t="n">
-        <v>6712137</v>
+        <v>6712101</v>
       </c>
       <c r="S35" t="n">
         <v>20</v>
@@ -3969,57 +3966,60 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130803082</v>
+        <v>130803040</v>
       </c>
       <c r="B36" t="n">
-        <v>83089</v>
+        <v>91937</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1312</v>
+        <v>5447</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Östra utsjö, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>424785</v>
+        <v>424793</v>
       </c>
       <c r="R36" t="n">
-        <v>6712249</v>
+        <v>6712247</v>
       </c>
       <c r="S36" t="n">
         <v>20</v>
@@ -4060,50 +4060,51 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>130803095</v>
+        <v>130803041</v>
       </c>
       <c r="B37" t="n">
-        <v>83215</v>
+        <v>91872</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>308</v>
+        <v>5447</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4113,10 +4114,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>424724</v>
+        <v>424881</v>
       </c>
       <c r="R37" t="n">
-        <v>6712378</v>
+        <v>6712113</v>
       </c>
       <c r="S37" t="n">
         <v>20</v>
@@ -4163,44 +4164,44 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>130803075</v>
+        <v>130803042</v>
       </c>
       <c r="B38" t="n">
-        <v>79243</v>
+        <v>91872</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4210,10 +4211,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>424923</v>
+        <v>424979</v>
       </c>
       <c r="R38" t="n">
-        <v>6712109</v>
+        <v>6712092</v>
       </c>
       <c r="S38" t="n">
         <v>20</v>
@@ -4260,60 +4261,60 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>130803100</v>
+        <v>131887804</v>
       </c>
       <c r="B39" t="n">
-        <v>83215</v>
+        <v>91937</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>308</v>
+        <v>5447</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Östra utsjö, Dlr</t>
+          <t>Nordvallen, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>424965</v>
+        <v>424727</v>
       </c>
       <c r="R39" t="n">
-        <v>6712084</v>
+        <v>6712355</v>
       </c>
       <c r="S39" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4337,12 +4338,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2026-03-22</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2026-03-22</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4357,68 +4358,60 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>130803045</v>
+        <v>131887805</v>
       </c>
       <c r="B40" t="n">
-        <v>57884</v>
+        <v>91937</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Östra utsjö, Dlr</t>
+          <t>Nordvallen, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>424768</v>
+        <v>424890</v>
       </c>
       <c r="R40" t="n">
-        <v>6712134</v>
+        <v>6712239</v>
       </c>
       <c r="S40" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4442,17 +4435,12 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2026-03-22</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>2026-03-22</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4467,65 +4455,57 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>130803050</v>
+        <v>130803071</v>
       </c>
       <c r="B41" t="n">
-        <v>57884</v>
+        <v>91282</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>5685</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Jülich</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Östra utsjö, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>424768</v>
+        <v>424873</v>
       </c>
       <c r="R41" t="n">
-        <v>6712278</v>
+        <v>6712126</v>
       </c>
       <c r="S41" t="n">
         <v>20</v>
@@ -4560,11 +4540,6 @@
           <t>2026-01-20</t>
         </is>
       </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
@@ -4577,65 +4552,57 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>130803059</v>
+        <v>130803073</v>
       </c>
       <c r="B42" t="n">
-        <v>57884</v>
+        <v>79327</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Östra utsjö, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>424858</v>
+        <v>424873</v>
       </c>
       <c r="R42" t="n">
-        <v>6712137</v>
+        <v>6712251</v>
       </c>
       <c r="S42" t="n">
         <v>20</v>
@@ -4670,11 +4637,6 @@
           <t>2026-01-20</t>
         </is>
       </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
@@ -4687,65 +4649,57 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>130803061</v>
+        <v>130803074</v>
       </c>
       <c r="B43" t="n">
-        <v>57884</v>
+        <v>79327</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Östra utsjö, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>424959</v>
+        <v>424801</v>
       </c>
       <c r="R43" t="n">
-        <v>6712127</v>
+        <v>6712403</v>
       </c>
       <c r="S43" t="n">
         <v>20</v>
@@ -4780,11 +4734,6 @@
           <t>2026-01-20</t>
         </is>
       </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
@@ -4797,65 +4746,57 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>130803051</v>
+        <v>130803075</v>
       </c>
       <c r="B44" t="n">
-        <v>57884</v>
+        <v>79327</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Östra utsjö, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>424785</v>
+        <v>424923</v>
       </c>
       <c r="R44" t="n">
-        <v>6712250</v>
+        <v>6712109</v>
       </c>
       <c r="S44" t="n">
         <v>20</v>
@@ -4890,11 +4831,6 @@
           <t>2026-01-20</t>
         </is>
       </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
@@ -4907,65 +4843,57 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>130803046</v>
+        <v>130803077</v>
       </c>
       <c r="B45" t="n">
-        <v>57884</v>
+        <v>79327</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Östra utsjö, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>424910</v>
+        <v>424877</v>
       </c>
       <c r="R45" t="n">
-        <v>6712215</v>
+        <v>6712121</v>
       </c>
       <c r="S45" t="n">
         <v>20</v>
@@ -5000,11 +4928,6 @@
           <t>2026-01-20</t>
         </is>
       </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
@@ -5017,65 +4940,57 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>130803058</v>
+        <v>130803078</v>
       </c>
       <c r="B46" t="n">
-        <v>57884</v>
+        <v>79327</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Östra utsjö, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>424867</v>
+        <v>424951</v>
       </c>
       <c r="R46" t="n">
-        <v>6712141</v>
+        <v>6712137</v>
       </c>
       <c r="S46" t="n">
         <v>20</v>
@@ -5110,11 +5025,6 @@
           <t>2026-01-20</t>
         </is>
       </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
@@ -5127,65 +5037,57 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>130803052</v>
+        <v>130803079</v>
       </c>
       <c r="B47" t="n">
-        <v>57884</v>
+        <v>79327</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Östra utsjö, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>424773</v>
+        <v>424980</v>
       </c>
       <c r="R47" t="n">
-        <v>6712133</v>
+        <v>6712107</v>
       </c>
       <c r="S47" t="n">
         <v>20</v>
@@ -5220,11 +5122,6 @@
           <t>2026-01-20</t>
         </is>
       </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
@@ -5237,65 +5134,57 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>130803049</v>
+        <v>130803066</v>
       </c>
       <c r="B48" t="n">
-        <v>57884</v>
+        <v>75300</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>6428</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Östra utsjö, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>424771</v>
+        <v>424814</v>
       </c>
       <c r="R48" t="n">
-        <v>6712443</v>
+        <v>6712218</v>
       </c>
       <c r="S48" t="n">
         <v>20</v>
@@ -5330,11 +5219,6 @@
           <t>2026-01-20</t>
         </is>
       </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
@@ -5347,65 +5231,57 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>130803060</v>
+        <v>130848916</v>
       </c>
       <c r="B49" t="n">
-        <v>57884</v>
+        <v>79351</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100109</v>
+        <v>6434</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Östra utsjö, Dlr</t>
+          <t>Nordvallen, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>424917</v>
+        <v>424579</v>
       </c>
       <c r="R49" t="n">
-        <v>6712165</v>
+        <v>6712188</v>
       </c>
       <c r="S49" t="n">
         <v>20</v>
@@ -5432,17 +5308,12 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5457,22 +5328,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>130803054</v>
+        <v>130803036</v>
       </c>
       <c r="B50" t="n">
-        <v>57884</v>
+        <v>83307</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5480,42 +5351,34 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Östra utsjö, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>424788</v>
+        <v>424756</v>
       </c>
       <c r="R50" t="n">
-        <v>6712134</v>
+        <v>6712130</v>
       </c>
       <c r="S50" t="n">
         <v>20</v>
@@ -5550,11 +5413,6 @@
           <t>2026-01-20</t>
         </is>
       </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD50" t="b">
         <v>0</v>
       </c>
@@ -5567,22 +5425,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>130803053</v>
+        <v>130803037</v>
       </c>
       <c r="B51" t="n">
-        <v>57884</v>
+        <v>83307</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5590,42 +5448,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Östra utsjö, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>424753</v>
+        <v>424874</v>
       </c>
       <c r="R51" t="n">
-        <v>6712126</v>
+        <v>6712082</v>
       </c>
       <c r="S51" t="n">
         <v>20</v>
@@ -5660,11 +5510,6 @@
           <t>2026-01-20</t>
         </is>
       </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
@@ -5677,22 +5522,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>130803047</v>
+        <v>130803039</v>
       </c>
       <c r="B52" t="n">
-        <v>57884</v>
+        <v>83307</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5700,42 +5545,34 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Östra utsjö, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>424836</v>
+        <v>424963</v>
       </c>
       <c r="R52" t="n">
-        <v>6712286</v>
+        <v>6712076</v>
       </c>
       <c r="S52" t="n">
         <v>20</v>
@@ -5770,11 +5607,6 @@
           <t>2026-01-20</t>
         </is>
       </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD52" t="b">
         <v>0</v>
       </c>
@@ -5787,22 +5619,22 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>130803044</v>
+        <v>130848929</v>
       </c>
       <c r="B53" t="n">
-        <v>57884</v>
+        <v>79084</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5810,42 +5642,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Östra utsjö, Dlr</t>
+          <t>Nordvallen, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>424933</v>
+        <v>424592</v>
       </c>
       <c r="R53" t="n">
-        <v>6712156</v>
+        <v>6712413</v>
       </c>
       <c r="S53" t="n">
         <v>20</v>
@@ -5872,17 +5696,12 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5897,22 +5716,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>130803056</v>
+        <v>131887903</v>
       </c>
       <c r="B54" t="n">
-        <v>57884</v>
+        <v>79130</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5920,45 +5739,37 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Östra utsjö, Dlr</t>
+          <t>Nordvallen, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>424852</v>
+        <v>424867</v>
       </c>
       <c r="R54" t="n">
-        <v>6712133</v>
+        <v>6712275</v>
       </c>
       <c r="S54" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -5982,17 +5793,12 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2026-03-22</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>2026-03-22</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6007,22 +5813,22 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>130803055</v>
+        <v>131887863</v>
       </c>
       <c r="B55" t="n">
-        <v>57884</v>
+        <v>79459</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6030,45 +5836,37 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100109</v>
+        <v>6450</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Östra utsjö, Dlr</t>
+          <t>Nordvallen, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>424839</v>
+        <v>424825</v>
       </c>
       <c r="R55" t="n">
-        <v>6712128</v>
+        <v>6712316</v>
       </c>
       <c r="S55" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6092,17 +5890,12 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2026-03-22</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>2026-03-22</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6117,22 +5910,22 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>130803048</v>
+        <v>131887866</v>
       </c>
       <c r="B56" t="n">
-        <v>57884</v>
+        <v>79459</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6140,45 +5933,37 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100109</v>
+        <v>6450</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Östra utsjö, Dlr</t>
+          <t>Nordvallen, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>424801</v>
+        <v>424879</v>
       </c>
       <c r="R56" t="n">
-        <v>6712325</v>
+        <v>6712233</v>
       </c>
       <c r="S56" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6202,17 +5987,12 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2026-03-22</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>2026-03-22</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6227,22 +6007,22 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>130803057</v>
+        <v>130848918</v>
       </c>
       <c r="B57" t="n">
-        <v>57884</v>
+        <v>80432</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6250,42 +6030,34 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Östra utsjö, Dlr</t>
+          <t>Nordvallen, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>424935</v>
+        <v>424636</v>
       </c>
       <c r="R57" t="n">
-        <v>6712079</v>
+        <v>6712522</v>
       </c>
       <c r="S57" t="n">
         <v>20</v>
@@ -6312,17 +6084,12 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6337,12 +6104,12 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
@@ -6352,7 +6119,7 @@
         <v>130848914</v>
       </c>
       <c r="B58" t="n">
-        <v>80378</v>
+        <v>80461</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6434,22 +6201,22 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>130848919</v>
+        <v>130803044</v>
       </c>
       <c r="B59" t="n">
-        <v>81229</v>
+        <v>57953</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6457,34 +6224,42 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1049</v>
+        <v>100109</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Nordvallen, Dlr</t>
+          <t>Östra utsjö, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>424721</v>
+        <v>424933</v>
       </c>
       <c r="R59" t="n">
-        <v>6712550</v>
+        <v>6712156</v>
       </c>
       <c r="S59" t="n">
         <v>20</v>
@@ -6511,12 +6286,17 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6531,57 +6311,65 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>130848925</v>
+        <v>130803045</v>
       </c>
       <c r="B60" t="n">
-        <v>80309</v>
+        <v>57953</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>229497</v>
+        <v>100109</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Nordvallen, Dlr</t>
+          <t>Östra utsjö, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>424635</v>
+        <v>424768</v>
       </c>
       <c r="R60" t="n">
-        <v>6712530</v>
+        <v>6712134</v>
       </c>
       <c r="S60" t="n">
         <v>20</v>
@@ -6608,12 +6396,17 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6628,22 +6421,22 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>130848907</v>
+        <v>130803046</v>
       </c>
       <c r="B61" t="n">
-        <v>57884</v>
+        <v>57953</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6673,20 +6466,20 @@
       <c r="L61" t="inlineStr"/>
       <c r="M61" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Nordvallen, Dlr</t>
+          <t>Östra utsjö, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>424588</v>
+        <v>424910</v>
       </c>
       <c r="R61" t="n">
-        <v>6712316</v>
+        <v>6712215</v>
       </c>
       <c r="S61" t="n">
         <v>20</v>
@@ -6713,12 +6506,12 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="AC61" t="inlineStr">
@@ -6738,22 +6531,22 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>130848917</v>
+        <v>130803047</v>
       </c>
       <c r="B62" t="n">
-        <v>79002</v>
+        <v>57953</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6761,34 +6554,42 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Nordvallen, Dlr</t>
+          <t>Östra utsjö, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>424590</v>
+        <v>424836</v>
       </c>
       <c r="R62" t="n">
-        <v>6712294</v>
+        <v>6712286</v>
       </c>
       <c r="S62" t="n">
         <v>20</v>
@@ -6815,12 +6616,17 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6835,22 +6641,22 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>130848921</v>
+        <v>130803048</v>
       </c>
       <c r="B63" t="n">
-        <v>81229</v>
+        <v>57953</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6858,34 +6664,42 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>1049</v>
+        <v>100109</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Nordvallen, Dlr</t>
+          <t>Östra utsjö, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>424593</v>
+        <v>424801</v>
       </c>
       <c r="R63" t="n">
-        <v>6712411</v>
+        <v>6712325</v>
       </c>
       <c r="S63" t="n">
         <v>20</v>
@@ -6912,12 +6726,17 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -6932,57 +6751,65 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>130848915</v>
+        <v>130803049</v>
       </c>
       <c r="B64" t="n">
-        <v>92268</v>
+        <v>57953</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Nordvallen, Dlr</t>
+          <t>Östra utsjö, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>424738</v>
+        <v>424771</v>
       </c>
       <c r="R64" t="n">
-        <v>6712212</v>
+        <v>6712443</v>
       </c>
       <c r="S64" t="n">
         <v>20</v>
@@ -7009,12 +6836,17 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7029,22 +6861,22 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>130848929</v>
+        <v>130803050</v>
       </c>
       <c r="B65" t="n">
-        <v>79001</v>
+        <v>57953</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7052,34 +6884,42 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Nordvallen, Dlr</t>
+          <t>Östra utsjö, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>424592</v>
+        <v>424768</v>
       </c>
       <c r="R65" t="n">
-        <v>6712413</v>
+        <v>6712278</v>
       </c>
       <c r="S65" t="n">
         <v>20</v>
@@ -7106,12 +6946,17 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7126,22 +6971,22 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>130848922</v>
+        <v>130803051</v>
       </c>
       <c r="B66" t="n">
-        <v>81229</v>
+        <v>57953</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7149,34 +6994,42 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>1049</v>
+        <v>100109</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Nordvallen, Dlr</t>
+          <t>Östra utsjö, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>424576</v>
+        <v>424785</v>
       </c>
       <c r="R66" t="n">
-        <v>6712311</v>
+        <v>6712250</v>
       </c>
       <c r="S66" t="n">
         <v>20</v>
@@ -7203,12 +7056,17 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7223,57 +7081,65 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>130848928</v>
+        <v>130803052</v>
       </c>
       <c r="B67" t="n">
-        <v>80309</v>
+        <v>57953</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>229497</v>
+        <v>100109</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Nordvallen, Dlr</t>
+          <t>Östra utsjö, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>424642</v>
+        <v>424773</v>
       </c>
       <c r="R67" t="n">
-        <v>6712433</v>
+        <v>6712133</v>
       </c>
       <c r="S67" t="n">
         <v>20</v>
@@ -7300,12 +7166,17 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7320,57 +7191,65 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>130848927</v>
+        <v>130803053</v>
       </c>
       <c r="B68" t="n">
-        <v>80309</v>
+        <v>57953</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>229497</v>
+        <v>100109</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Nordvallen, Dlr</t>
+          <t>Östra utsjö, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>424627</v>
+        <v>424753</v>
       </c>
       <c r="R68" t="n">
-        <v>6712461</v>
+        <v>6712126</v>
       </c>
       <c r="S68" t="n">
         <v>20</v>
@@ -7397,12 +7276,17 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7417,22 +7301,22 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>130848920</v>
+        <v>130803054</v>
       </c>
       <c r="B69" t="n">
-        <v>81229</v>
+        <v>57953</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7440,34 +7324,42 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>1049</v>
+        <v>100109</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Nordvallen, Dlr</t>
+          <t>Östra utsjö, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>424620</v>
+        <v>424788</v>
       </c>
       <c r="R69" t="n">
-        <v>6712420</v>
+        <v>6712134</v>
       </c>
       <c r="S69" t="n">
         <v>20</v>
@@ -7494,12 +7386,17 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7514,57 +7411,65 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>130848926</v>
+        <v>130803055</v>
       </c>
       <c r="B70" t="n">
-        <v>80309</v>
+        <v>57953</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>229497</v>
+        <v>100109</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Nordvallen, Dlr</t>
+          <t>Östra utsjö, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>424630</v>
+        <v>424839</v>
       </c>
       <c r="R70" t="n">
-        <v>6712465</v>
+        <v>6712128</v>
       </c>
       <c r="S70" t="n">
         <v>20</v>
@@ -7591,12 +7496,17 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7611,22 +7521,22 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>130848918</v>
+        <v>130803056</v>
       </c>
       <c r="B71" t="n">
-        <v>80349</v>
+        <v>57953</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7634,34 +7544,42 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Nordvallen, Dlr</t>
+          <t>Östra utsjö, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>424636</v>
+        <v>424852</v>
       </c>
       <c r="R71" t="n">
-        <v>6712522</v>
+        <v>6712133</v>
       </c>
       <c r="S71" t="n">
         <v>20</v>
@@ -7688,12 +7606,17 @@
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7708,44 +7631,44 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>130803063</v>
+        <v>130803057</v>
       </c>
       <c r="B72" t="n">
-        <v>57073</v>
+        <v>57953</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7753,7 +7676,7 @@
       <c r="L72" t="inlineStr"/>
       <c r="M72" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N72" t="inlineStr"/>
@@ -7763,10 +7686,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>424847</v>
+        <v>424935</v>
       </c>
       <c r="R72" t="n">
-        <v>6712117</v>
+        <v>6712079</v>
       </c>
       <c r="S72" t="n">
         <v>20</v>
@@ -7803,7 +7726,7 @@
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>Tjädertall</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -7818,44 +7741,44 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>130803062</v>
+        <v>130803058</v>
       </c>
       <c r="B73" t="n">
-        <v>57073</v>
+        <v>57953</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7863,7 +7786,7 @@
       <c r="L73" t="inlineStr"/>
       <c r="M73" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N73" t="inlineStr"/>
@@ -7873,10 +7796,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>424945</v>
+        <v>424867</v>
       </c>
       <c r="R73" t="n">
-        <v>6712147</v>
+        <v>6712141</v>
       </c>
       <c r="S73" t="n">
         <v>20</v>
@@ -7913,7 +7836,7 @@
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>Tjädertall</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -7928,22 +7851,22 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>130849489</v>
+        <v>130803059</v>
       </c>
       <c r="B74" t="n">
-        <v>80356</v>
+        <v>57953</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7951,34 +7874,42 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
+      <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr"/>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Nordvallen, Dlr</t>
+          <t>Östra utsjö, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>424637</v>
+        <v>424858</v>
       </c>
       <c r="R74" t="n">
-        <v>6712469</v>
+        <v>6712137</v>
       </c>
       <c r="S74" t="n">
         <v>20</v>
@@ -8005,12 +7936,17 @@
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8025,60 +7961,68 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>131887863</v>
+        <v>130803060</v>
       </c>
       <c r="B75" t="n">
-        <v>79405</v>
+        <v>57953</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6450</v>
+        <v>100109</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
+      <c r="K75" t="inlineStr"/>
+      <c r="L75" t="inlineStr"/>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Nordvallen, Dlr</t>
+          <t>Östra utsjö, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>424825</v>
+        <v>424917</v>
       </c>
       <c r="R75" t="n">
-        <v>6712316</v>
+        <v>6712165</v>
       </c>
       <c r="S75" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8102,12 +8046,17 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8134,10 +8083,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>131888941</v>
+        <v>130803061</v>
       </c>
       <c r="B76" t="n">
-        <v>57949</v>
+        <v>57953</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8167,7 +8116,7 @@
       <c r="L76" t="inlineStr"/>
       <c r="M76" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N76" t="inlineStr"/>
@@ -8177,10 +8126,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>424979</v>
+        <v>424959</v>
       </c>
       <c r="R76" t="n">
-        <v>6712092</v>
+        <v>6712127</v>
       </c>
       <c r="S76" t="n">
         <v>20</v>
@@ -8207,12 +8156,17 @@
       </c>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8239,10 +8193,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>131887913</v>
+        <v>130848907</v>
       </c>
       <c r="B77" t="n">
-        <v>85525</v>
+        <v>57953</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8250,37 +8204,45 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>241</v>
+        <v>100109</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Gransotdyna</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Camarops tubulina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Shear</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
+      <c r="K77" t="inlineStr"/>
+      <c r="L77" t="inlineStr"/>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
           <t>Nordvallen, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>424733</v>
+        <v>424588</v>
       </c>
       <c r="R77" t="n">
-        <v>6712369</v>
+        <v>6712316</v>
       </c>
       <c r="S77" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -8304,12 +8266,17 @@
       </c>
       <c r="Y77" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2026-01-23</t>
+        </is>
+      </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8318,7 +8285,6 @@
       <c r="AE77" t="b">
         <v>0</v>
       </c>
-      <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="b">
         <v>0</v>
       </c>
@@ -8337,48 +8303,56 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>131887805</v>
+        <v>131888941</v>
       </c>
       <c r="B78" t="n">
-        <v>91861</v>
+        <v>57975</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
+      <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr"/>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Nordvallen, Dlr</t>
+          <t>Östra utsjö, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>424890</v>
+        <v>424979</v>
       </c>
       <c r="R78" t="n">
-        <v>6712239</v>
+        <v>6712092</v>
       </c>
       <c r="S78" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -8402,12 +8376,12 @@
       </c>
       <c r="Y78" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8434,48 +8408,56 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>131887962</v>
+        <v>130803062</v>
       </c>
       <c r="B79" t="n">
-        <v>83291</v>
+        <v>57141</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>308</v>
+        <v>100138</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
+      <c r="K79" t="inlineStr"/>
+      <c r="L79" t="inlineStr"/>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Nordvallen, Dlr</t>
+          <t>Östra utsjö, Dlr</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>424920</v>
+        <v>424945</v>
       </c>
       <c r="R79" t="n">
-        <v>6712232</v>
+        <v>6712147</v>
       </c>
       <c r="S79" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -8499,12 +8481,17 @@
       </c>
       <c r="Y79" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>Tjädertall</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8531,48 +8518,56 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>131887903</v>
+        <v>130803063</v>
       </c>
       <c r="B80" t="n">
-        <v>79076</v>
+        <v>57141</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6446</v>
+        <v>100138</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
+      <c r="K80" t="inlineStr"/>
+      <c r="L80" t="inlineStr"/>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Nordvallen, Dlr</t>
+          <t>Östra utsjö, Dlr</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>424867</v>
+        <v>424847</v>
       </c>
       <c r="R80" t="n">
-        <v>6712275</v>
+        <v>6712117</v>
       </c>
       <c r="S80" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -8596,12 +8591,17 @@
       </c>
       <c r="Y80" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>Tjädertall</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8628,10 +8628,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>131887967</v>
+        <v>130803067</v>
       </c>
       <c r="B81" t="n">
-        <v>83291</v>
+        <v>78339</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8639,37 +8639,37 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>308</v>
+        <v>228579</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Nordvallen, Dlr</t>
+          <t>Östra utsjö, Dlr</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>424723</v>
+        <v>424814</v>
       </c>
       <c r="R81" t="n">
-        <v>6712381</v>
+        <v>6712361</v>
       </c>
       <c r="S81" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -8693,12 +8693,12 @@
       </c>
       <c r="Y81" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -8725,10 +8725,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>131887961</v>
+        <v>130848917</v>
       </c>
       <c r="B82" t="n">
-        <v>83291</v>
+        <v>79085</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8736,21 +8736,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>308</v>
+        <v>228912</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8760,13 +8760,13 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>424831</v>
+        <v>424590</v>
       </c>
       <c r="R82" t="n">
-        <v>6712360</v>
+        <v>6712294</v>
       </c>
       <c r="S82" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -8790,12 +8790,12 @@
       </c>
       <c r="Y82" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -8822,32 +8822,32 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>131887866</v>
+        <v>131887893</v>
       </c>
       <c r="B83" t="n">
-        <v>79405</v>
+        <v>79131</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6450</v>
+        <v>228912</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8857,10 +8857,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>424879</v>
+        <v>424556</v>
       </c>
       <c r="R83" t="n">
-        <v>6712233</v>
+        <v>6712375</v>
       </c>
       <c r="S83" t="n">
         <v>25</v>
@@ -8919,32 +8919,32 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>131887893</v>
+        <v>130848925</v>
       </c>
       <c r="B84" t="n">
-        <v>79077</v>
+        <v>80392</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>228912</v>
+        <v>229497</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -8954,13 +8954,13 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>424556</v>
+        <v>424635</v>
       </c>
       <c r="R84" t="n">
-        <v>6712375</v>
+        <v>6712530</v>
       </c>
       <c r="S84" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -8984,12 +8984,12 @@
       </c>
       <c r="Y84" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9016,10 +9016,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>131887804</v>
+        <v>130848926</v>
       </c>
       <c r="B85" t="n">
-        <v>91861</v>
+        <v>80392</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9027,21 +9027,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>5447</v>
+        <v>229497</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9051,13 +9051,13 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>424727</v>
+        <v>424630</v>
       </c>
       <c r="R85" t="n">
-        <v>6712355</v>
+        <v>6712465</v>
       </c>
       <c r="S85" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -9081,12 +9081,12 @@
       </c>
       <c r="Y85" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9110,6 +9110,200 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>130848927</v>
+      </c>
+      <c r="B86" t="n">
+        <v>80392</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>Nordvallen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q86" t="n">
+        <v>424627</v>
+      </c>
+      <c r="R86" t="n">
+        <v>6712461</v>
+      </c>
+      <c r="S86" t="n">
+        <v>20</v>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W86" t="inlineStr">
+        <is>
+          <t>Malung</t>
+        </is>
+      </c>
+      <c r="Y86" t="inlineStr">
+        <is>
+          <t>2026-01-23</t>
+        </is>
+      </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>2026-01-23</t>
+        </is>
+      </c>
+      <c r="AD86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT86" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX86" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>130848928</v>
+      </c>
+      <c r="B87" t="n">
+        <v>80392</v>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>Nordvallen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q87" t="n">
+        <v>424642</v>
+      </c>
+      <c r="R87" t="n">
+        <v>6712433</v>
+      </c>
+      <c r="S87" t="n">
+        <v>20</v>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W87" t="inlineStr">
+        <is>
+          <t>Malung</t>
+        </is>
+      </c>
+      <c r="Y87" t="inlineStr">
+        <is>
+          <t>2026-01-23</t>
+        </is>
+      </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>2026-01-23</t>
+        </is>
+      </c>
+      <c r="AD87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT87" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX87" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY87" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 1481-2026 artfynd.xlsx
+++ b/artfynd/A 1481-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY87"/>
+  <dimension ref="A1:AZ87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130803065</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -867,6 +877,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131887913</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -968,6 +983,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130803072</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1065,6 +1085,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130803093</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1162,6 +1187,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130803094</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1259,6 +1289,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130803095</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1356,6 +1391,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130803096</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1453,6 +1493,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130803097</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1550,6 +1595,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130803098</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1647,6 +1697,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130803099</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1744,6 +1799,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130803100</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1841,6 +1901,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131887961</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1938,6 +2003,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131887962</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2035,6 +2105,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131887967</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2132,6 +2207,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130803068</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2229,6 +2309,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130803092</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2326,6 +2411,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130803069</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2423,6 +2513,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130848919</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2520,6 +2615,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130848920</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2617,6 +2717,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130848921</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2714,6 +2819,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130848922</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2811,6 +2921,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130848915</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2908,6 +3023,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130803080</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3005,6 +3125,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130803081</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3102,6 +3227,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130803082</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3199,6 +3329,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130803083</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3296,6 +3431,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130803084</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3393,6 +3533,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130803085</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3490,6 +3635,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130803086</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3587,6 +3737,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130803087</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3684,6 +3839,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130803088</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3781,6 +3941,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130849489</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3878,6 +4043,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130803043</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -3975,6 +4145,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130803064</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4076,6 +4251,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130803040</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4173,6 +4353,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130803041</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4270,6 +4455,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130803042</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4367,6 +4557,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131887804</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4464,6 +4659,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131887805</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4561,6 +4761,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130803071</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4658,6 +4863,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130803073</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4755,6 +4965,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130803074</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -4852,6 +5067,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130803075</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -4949,6 +5169,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130803077</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5046,6 +5271,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130803078</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5143,6 +5373,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130803079</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5240,6 +5475,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130803066</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5337,6 +5577,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130848916</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5434,6 +5679,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130803036</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5531,6 +5781,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130803037</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5628,6 +5883,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130803039</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -5725,6 +5985,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130848929</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -5822,6 +6087,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131887903</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -5919,6 +6189,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131887863</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6016,6 +6291,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131887866</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6113,6 +6393,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130848918</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6210,6 +6495,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130848914</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6320,6 +6610,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130803044</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6430,6 +6725,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130803045</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6540,6 +6840,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130803046</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -6650,6 +6955,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130803047</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -6760,6 +7070,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130803048</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -6870,6 +7185,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130803049</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -6980,6 +7300,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130803050</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7090,6 +7415,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130803051</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7200,6 +7530,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130803052</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7310,6 +7645,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130803053</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7420,6 +7760,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130803054</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -7530,6 +7875,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130803055</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -7640,6 +7990,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130803056</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -7750,6 +8105,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130803057</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -7860,6 +8220,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130803058</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -7970,6 +8335,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130803059</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8080,6 +8450,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130803060</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8190,6 +8565,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130803061</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8300,6 +8680,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130848907</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8405,6 +8790,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131888941</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -8515,6 +8905,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130803062</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -8625,6 +9020,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130803063</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -8722,6 +9122,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130803067</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -8819,6 +9224,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130848917</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -8916,6 +9326,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131887893</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -9013,6 +9428,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130848925</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -9110,6 +9530,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130848926</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -9207,6 +9632,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130848927</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -9304,8 +9734,101 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130848928</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>